--- a/Planilhas/Diagnostico.xlsx
+++ b/Planilhas/Diagnostico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/FOMENTO-ONASP/FOMENTO-ONASP/Planilhas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0483DE74-CA1B-4285-9071-A45D6A3DFCAA}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84897353-282A-48E7-A0E4-8467C6C2ED0F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2669,9 +2669,21 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:CJ30" totalsRowShown="0">
-  <autoFilter ref="A1:CJ30" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:CJ30" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="MG"/>
+        <filter val="RR"/>
+        <filter val="RS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="88">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="87"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora de início" dataDxfId="86"/>
@@ -3066,7 +3078,9 @@
   <dimension ref="A1:CJ30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="88" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.6640625" customWidth="1"/>
+    <col min="8" max="88" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:88" x14ac:dyDescent="0.3">
@@ -3335,7 +3349,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3595,7 +3609,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3852,7 +3866,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4112,7 +4126,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4372,7 +4386,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4623,7 +4637,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4880,7 +4894,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5131,7 +5145,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5391,7 +5405,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5651,7 +5665,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5914,7 +5928,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6177,7 +6191,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6437,7 +6451,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6700,7 +6714,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6963,7 +6977,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7226,7 +7240,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="17" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7483,7 +7497,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="18" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7746,7 +7760,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="19" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8009,7 +8023,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="20" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8269,7 +8283,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="21" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8532,7 +8546,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="22" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -9043,7 +9057,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="24" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -9560,7 +9574,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="26" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -9823,7 +9837,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="27" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -10086,7 +10100,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -10585,7 +10599,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="30" spans="1:88" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:88" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
